--- a/Tuning/Tuning_Model_NBinom.xlsx
+++ b/Tuning/Tuning_Model_NBinom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Documents\GitHub\mortality_data_pr\Tuning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B773D61-DA96-4407-8A24-9B21017E3C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49962009-4C6C-4DA8-B23D-A8CC4DCCB37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>Fecha</t>
   </si>
@@ -60,6 +60,9 @@
     <t>Muestras</t>
   </si>
   <si>
+    <t>T10</t>
+  </si>
+  <si>
     <t>Ambos</t>
   </si>
   <si>
@@ -70,14 +73,33 @@
   </si>
   <si>
     <t>T3</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>T6</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>T8</t>
+  </si>
+  <si>
+    <t>T9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -136,7 +158,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -159,12 +181,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -189,40 +224,73 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="21" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="21" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -563,17 +631,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="12.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="1" customWidth="1"/>
-    <col min="12" max="16" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="12.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="30" width="12.44140625" style="1" customWidth="1"/>
     <col min="31" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -584,7 +660,7 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -625,117 +701,117 @@
       <c r="A2" s="7">
         <v>46237</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="28">
         <v>0.53083333333333338</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12">
-        <v>1</v>
-      </c>
-      <c r="G2" s="12">
+      <c r="C2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="21">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21">
+        <v>1</v>
+      </c>
+      <c r="G2" s="21">
         <v>10</v>
       </c>
-      <c r="H2" s="12">
-        <v>1</v>
-      </c>
-      <c r="I2" s="14">
-        <v>1</v>
-      </c>
-      <c r="J2" s="14">
+      <c r="H2" s="21">
+        <v>1</v>
+      </c>
+      <c r="I2" s="22">
+        <v>1</v>
+      </c>
+      <c r="J2" s="22">
         <v>10</v>
       </c>
-      <c r="K2" s="14">
-        <v>1</v>
-      </c>
-      <c r="L2" s="12">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12">
+      <c r="K2" s="22">
+        <v>1</v>
+      </c>
+      <c r="L2" s="21">
+        <v>1</v>
+      </c>
+      <c r="M2" s="21">
         <v>10</v>
       </c>
-      <c r="N2" s="12">
-        <v>1</v>
-      </c>
-      <c r="O2" s="15">
-        <v>1</v>
-      </c>
-      <c r="P2" s="15">
+      <c r="N2" s="21">
+        <v>1</v>
+      </c>
+      <c r="O2" s="23">
+        <v>1</v>
+      </c>
+      <c r="P2" s="23">
         <v>10</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="29">
         <v>91.168091168091095</v>
       </c>
-      <c r="R2" s="16">
+      <c r="R2" s="29">
         <v>96.866096866096797</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="8">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="14">
         <v>46237</v>
       </c>
       <c r="B3" s="9">
         <v>0.65849537037037043</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12">
-        <v>1</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="E3" s="24">
+        <v>1</v>
+      </c>
+      <c r="F3" s="24">
+        <v>1</v>
+      </c>
+      <c r="G3" s="24">
         <v>10</v>
       </c>
-      <c r="H3" s="12">
-        <v>1</v>
-      </c>
-      <c r="I3" s="14">
-        <v>1</v>
-      </c>
-      <c r="J3" s="14">
+      <c r="H3" s="24">
+        <v>1</v>
+      </c>
+      <c r="I3" s="25">
+        <v>1</v>
+      </c>
+      <c r="J3" s="25">
         <v>10</v>
       </c>
-      <c r="K3" s="14">
-        <v>1</v>
-      </c>
-      <c r="L3" s="12">
-        <v>1</v>
-      </c>
-      <c r="M3" s="12">
+      <c r="K3" s="25">
+        <v>1</v>
+      </c>
+      <c r="L3" s="24">
+        <v>1</v>
+      </c>
+      <c r="M3" s="24">
         <v>10</v>
       </c>
-      <c r="N3" s="12">
-        <v>1</v>
-      </c>
-      <c r="O3" s="15">
-        <v>1</v>
-      </c>
-      <c r="P3" s="15">
+      <c r="N3" s="24">
+        <v>1</v>
+      </c>
+      <c r="O3" s="26">
+        <v>1</v>
+      </c>
+      <c r="P3" s="26">
         <v>10</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="30">
         <v>92.877492877492799</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="30">
         <v>97.578347578347504</v>
       </c>
-      <c r="S3" s="13">
+      <c r="S3" s="20">
         <v>1000</v>
       </c>
     </row>
@@ -743,72 +819,473 @@
       <c r="A4" s="7">
         <v>46237</v>
       </c>
-      <c r="B4" s="9">
-        <v>0.69809027777777777</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="12">
-        <v>1</v>
-      </c>
-      <c r="F4" s="12">
-        <v>1</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="B4" s="17">
+        <v>0.70431712962962967</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="21">
+        <v>1</v>
+      </c>
+      <c r="F4" s="21">
+        <v>1</v>
+      </c>
+      <c r="G4" s="21">
         <v>100</v>
       </c>
-      <c r="H4" s="12">
-        <v>1</v>
-      </c>
-      <c r="I4" s="14">
-        <v>1</v>
-      </c>
-      <c r="J4" s="14">
+      <c r="H4" s="21">
+        <v>1</v>
+      </c>
+      <c r="I4" s="22">
+        <v>1</v>
+      </c>
+      <c r="J4" s="22">
         <v>100</v>
       </c>
-      <c r="K4" s="14">
-        <v>1</v>
-      </c>
-      <c r="L4" s="12">
-        <v>1</v>
-      </c>
-      <c r="M4" s="12">
+      <c r="K4" s="22">
+        <v>1</v>
+      </c>
+      <c r="L4" s="21">
+        <v>1</v>
+      </c>
+      <c r="M4" s="21">
         <v>100</v>
       </c>
-      <c r="N4" s="12">
-        <v>1</v>
-      </c>
-      <c r="O4" s="15">
-        <v>1</v>
-      </c>
-      <c r="P4" s="15">
+      <c r="N4" s="21">
+        <v>1</v>
+      </c>
+      <c r="O4" s="23">
+        <v>1</v>
+      </c>
+      <c r="P4" s="23">
         <v>100</v>
       </c>
-      <c r="S4" s="1">
+      <c r="Q4" s="18">
+        <v>91.168091169999997</v>
+      </c>
+      <c r="R4" s="18">
+        <v>96.866096870000007</v>
+      </c>
+      <c r="S4" s="8">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C5" s="10"/>
+      <c r="A5" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B5" s="17">
+        <v>0.74063657407407413</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="21">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21">
+        <v>100</v>
+      </c>
+      <c r="H5" s="21">
+        <v>1</v>
+      </c>
+      <c r="I5" s="22">
+        <v>1</v>
+      </c>
+      <c r="J5" s="22">
+        <v>100</v>
+      </c>
+      <c r="K5" s="22">
+        <v>1</v>
+      </c>
+      <c r="L5" s="21">
+        <v>1</v>
+      </c>
+      <c r="M5" s="21">
+        <v>100</v>
+      </c>
+      <c r="N5" s="21">
+        <v>1</v>
+      </c>
+      <c r="O5" s="23">
+        <v>1</v>
+      </c>
+      <c r="P5" s="23">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>92.735042735042697</v>
+      </c>
+      <c r="R5" s="19">
+        <v>97.1509971509971</v>
+      </c>
+      <c r="S5" s="8">
+        <v>1000</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C6" s="10"/>
+      <c r="A6" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B6" s="17">
+        <v>0.74576388888888889</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="8">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P6" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>90.455840455840402</v>
+      </c>
+      <c r="R6" s="19">
+        <v>97.1509971509971</v>
+      </c>
+      <c r="S6" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C7" s="10"/>
+      <c r="A7" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B7" s="17">
+        <v>0.86120370370370369</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M7" s="8">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P7" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="R7" s="19">
+        <v>97.293447293447201</v>
+      </c>
+      <c r="S7" s="8">
+        <v>1000</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C8" s="10"/>
+      <c r="A8" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B8" s="17">
+        <v>0.95454861111111111</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="21">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21">
+        <v>1</v>
+      </c>
+      <c r="G8" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="21">
+        <v>1</v>
+      </c>
+      <c r="I8" s="22">
+        <v>1</v>
+      </c>
+      <c r="J8" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="22">
+        <v>1</v>
+      </c>
+      <c r="L8" s="21">
+        <v>1</v>
+      </c>
+      <c r="M8" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="N8" s="21">
+        <v>1</v>
+      </c>
+      <c r="O8" s="23">
+        <v>1</v>
+      </c>
+      <c r="P8" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>91.168091168091095</v>
+      </c>
+      <c r="R8" s="19">
+        <v>97.435897435897402</v>
+      </c>
+      <c r="S8" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C9" s="10"/>
+      <c r="A9" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B9" s="17">
+        <v>0.98827546296296298</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="21">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="21">
+        <v>1</v>
+      </c>
+      <c r="I9" s="22">
+        <v>1</v>
+      </c>
+      <c r="J9" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="22">
+        <v>1</v>
+      </c>
+      <c r="L9" s="21">
+        <v>1</v>
+      </c>
+      <c r="M9" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="21">
+        <v>1</v>
+      </c>
+      <c r="O9" s="23">
+        <v>1</v>
+      </c>
+      <c r="P9" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>93.019943019943</v>
+      </c>
+      <c r="R9" s="19">
+        <v>97.1509971509971</v>
+      </c>
+      <c r="S9" s="8">
+        <v>1000</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C10" s="10"/>
+      <c r="A10" s="7">
+        <v>46238</v>
+      </c>
+      <c r="B10" s="17">
+        <v>3.5254629629629629E-2</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="21">
+        <v>1</v>
+      </c>
+      <c r="F10" s="21">
+        <v>1</v>
+      </c>
+      <c r="G10" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="H10" s="21">
+        <v>1</v>
+      </c>
+      <c r="I10" s="22">
+        <v>1</v>
+      </c>
+      <c r="J10" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="K10" s="22">
+        <v>1</v>
+      </c>
+      <c r="L10" s="21">
+        <v>1</v>
+      </c>
+      <c r="M10" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="N10" s="21">
+        <v>1</v>
+      </c>
+      <c r="O10" s="23">
+        <v>1</v>
+      </c>
+      <c r="P10" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>93.162393162393101</v>
+      </c>
+      <c r="R10" s="19">
+        <v>97.435897435897402</v>
+      </c>
+      <c r="S10" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>46238</v>
+      </c>
+      <c r="B11" s="17">
+        <v>4.0219907407407406E-2</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="21">
+        <v>1</v>
+      </c>
+      <c r="F11" s="21">
+        <v>1</v>
+      </c>
+      <c r="G11" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="21">
+        <v>1</v>
+      </c>
+      <c r="I11" s="22">
+        <v>1</v>
+      </c>
+      <c r="J11" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="K11" s="22">
+        <v>1</v>
+      </c>
+      <c r="L11" s="21">
+        <v>1</v>
+      </c>
+      <c r="M11" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="N11" s="21">
+        <v>1</v>
+      </c>
+      <c r="O11" s="23">
+        <v>1</v>
+      </c>
+      <c r="P11" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>91.310541310541296</v>
+      </c>
+      <c r="R11" s="19">
+        <v>97.008547008546998</v>
+      </c>
+      <c r="S11" s="8">
+        <v>1000</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
